--- a/sra_submission/Cheng_TGN_SRA_metadata.xlsx
+++ b/sra_submission/Cheng_TGN_SRA_metadata.xlsx
@@ -2168,7 +2168,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pooled human DRG RNA comparator material was supplied as RNA. RNA underwent bead-based poly(A) selection, cDNA synthesis, and PCR amplification with the VAHTS Universal V10 RNA-seq Library Prep Kit for Illumina (Vazyme #NR606-02). Equimolar libraries were sequenced as 150-bp paired-end reads on an Illumina NovaSeq X Plus.</t>
+          <t>One of two separate lots of pooled human DRG total RNA was supplied by Takara Bio (Cat# 636150; normal donors aged 16-65 years). RNA underwent bead-based poly(A) selection, cDNA synthesis, and PCR amplification with the VAHTS Universal V10 RNA-seq Library Prep Kit for Illumina (Vazyme #NR606-02). Equimolar libraries were sequenced as 150-bp paired-end reads on an Illumina NovaSeq X Plus.</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pooled human DRG RNA comparator material was supplied as RNA. RNA underwent bead-based poly(A) selection, cDNA synthesis, and PCR amplification with the VAHTS Universal V10 RNA-seq Library Prep Kit for Illumina (Vazyme #NR606-02). Equimolar libraries were sequenced as 150-bp paired-end reads on an Illumina NovaSeq X Plus.</t>
+          <t>One of two separate lots of pooled human DRG total RNA was supplied by Takara Bio (Cat# 636150; normal donors aged 16-65 years). RNA underwent bead-based poly(A) selection, cDNA synthesis, and PCR amplification with the VAHTS Universal V10 RNA-seq Library Prep Kit for Illumina (Vazyme #NR606-02). Equimolar libraries were sequenced as 150-bp paired-end reads on an Illumina NovaSeq X Plus.</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
